--- a/results/andar_할인율모니터링_20260806.xlsx
+++ b/results/andar_할인율모니터링_20260806.xlsx
@@ -461,126 +461,126 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5845&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15432&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EJFMT-01</t>
+          <t>ENTSC-12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>릴렉스 에어소프트 요가매트 (8mm)</t>
+          <t>[1&amp;1] 논슬립 퍼포먼스 토삭스</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>25,800</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>27,000</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>9,903</t>
+          <t>3,366</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16629&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15432&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EPTET-01</t>
+          <t>EOTSC-15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>언더웨어 파우치</t>
+          <t>[1&amp;1] 논슬립 퍼포먼스 토삭스</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>25,800</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>3,366</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16629&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EPTSC-04</t>
+          <t>EPTET-01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[3 SET] 필라테스 삭스</t>
+          <t>언더웨어 파우치</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41,700</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30,900</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>295</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EPTSC-05</t>
+          <t>EPTSC-04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EPTSC-06</t>
+          <t>EPTSC-05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -671,126 +671,126 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5145&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EJPFR-04</t>
+          <t>EPTSC-06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>릴렉스 폼롤러 Ⅱ</t>
+          <t>[3 SET] 필라테스 삭스</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>41,700</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>30,900</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6,335</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15432&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5145&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ENTSC-12</t>
+          <t>EJPFR-04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 퍼포먼스 토삭스</t>
+          <t>릴렉스 폼롤러 Ⅱ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>25,800</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3,364</t>
+          <t>6,335</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15432&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5845&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EOTSC-15</t>
+          <t>EJFMT-01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 퍼포먼스 토삭스</t>
+          <t>릴렉스 에어소프트 요가매트 (8mm)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>25,800</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3,364</t>
+          <t>9,906</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7,098</t>
+          <t>7,100</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1,057</t>
+          <t>1,061</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1175,121 +1175,121 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17857&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14563&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EPTSC-03</t>
+          <t>EOTMK-01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[1&amp;1] 데일리 루즈 삭스</t>
+          <t>UV 프로텍션 골프 마스크 (벨크로)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18,900</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1,044</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14563&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17414&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EOTMK-01</t>
+          <t>EPTBG-01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UV 프로텍션 골프 마스크 (벨크로)</t>
+          <t>에어플라이 프리런 러닝 벨트</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>37,000</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1,039</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13852&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11110&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EOTET-03</t>
+          <t>ENTCP-01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>라이트 러닝 베스트</t>
+          <t>와이드 셰이드 버킷햇</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>67,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>678</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1301,79 +1301,79 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17414&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17857&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EPTBG-01</t>
+          <t>EPTSC-03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>에어플라이 프리런 러닝 벨트</t>
+          <t>[1&amp;1] 데일리 루즈 삭스</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>37,000</t>
+          <t>18,900</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11110&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13852&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ENTCP-01</t>
+          <t>EOTET-03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>와이드 셰이드 버킷햇</t>
+          <t>라이트 러닝 베스트</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>67,000</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>87</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1385,27 +1385,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15629&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16636&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EOTBG-23</t>
+          <t>EPTFB-01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>안다르 실버 리유저블백</t>
+          <t>퍼포먼스 심리스 헤드밴드</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1415,39 +1415,39 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12487&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15629&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ENTBG-18</t>
+          <t>EOTBG-23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>시티 플로우 빅 숄더백</t>
+          <t>안다르 실버 리유저블백</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>6,500</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>6,500</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>310</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1469,79 +1469,79 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16636&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13215&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EPTFB-01</t>
+          <t>EOTCP-01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>퍼포먼스 심리스 헤드밴드</t>
+          <t>올라운드 버킷햇</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>330</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13215&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12487&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EOTCP-01</t>
+          <t>ENTBG-18</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>올라운드 버킷햇</t>
+          <t>시티 플로우 빅 숄더백</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>438</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1553,205 +1553,205 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15372&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EOTSV-04</t>
+          <t>EOTBG-16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>프리런 라이트 러닝 밴드</t>
+          <t>폴더블 미니백 2.0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>22,000</t>
+          <t>33,000</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>192</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15372&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EOTBG-16</t>
+          <t>EOTSV-04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>폴더블 미니백 2.0</t>
+          <t>프리런 라이트 러닝 밴드</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>33,000</t>
+          <t>22,000</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10478&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14562&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ENTBG-05</t>
+          <t>EOTBG-11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>미니 숄더 앤 크로스백</t>
+          <t>메쉬 파우치</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>28,000</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4,926</t>
+          <t>179</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14562&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15350&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EOTBG-11</t>
+          <t>EOTSC-09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>메쉬 파우치</t>
+          <t>[1&amp;1] 컴프레션 러닝 니삭스</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>28,000</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>621</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15350&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10478&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EOTSC-09</t>
+          <t>ENTBG-05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[1&amp;1] 컴프레션 러닝 니삭스</t>
+          <t>미니 숄더 앤 크로스백</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>4,926</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1763,37 +1763,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5144&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14059&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EJPMS-05</t>
+          <t>ENTSO-02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>릴렉스 마사지 스틱 Ⅱ</t>
+          <t>안다르 제트플라이 (우먼즈)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>9,500</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>10,252</t>
+          <t>1,002</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1805,79 +1805,79 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13862&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14059&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EOTBG-03</t>
+          <t>ENTSO-12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>데이 앤 트래블 숄더백</t>
+          <t>안다르 제트플라이 (우먼즈)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>67,000</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>1,002</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5144&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EMTSC-04</t>
+          <t>EJPMS-05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
+          <t>릴렉스 마사지 스틱 Ⅱ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>15,800</t>
+          <t>9,500</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3,113</t>
+          <t>10,255</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EMTSC-05</t>
+          <t>EMTSC-04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>3,113</t>
+          <t>3,115</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1931,37 +1931,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14059&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8819&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ENTSO-02</t>
+          <t>EMTSC-05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>안다르 제트플라이 (우먼즈)</t>
+          <t>[1&amp;1] 논슬립 서포트 하프 토삭스 (HOLE &amp; SOLID)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>19,800</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>15,800</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1,001</t>
+          <t>3,115</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1973,153 +1973,153 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14059&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13862&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ENTSO-12</t>
+          <t>EOTBG-03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>안다르 제트플라이 (우먼즈)</t>
+          <t>데이 앤 트래블 숄더백</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>67,000</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1,001</t>
+          <t>111</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13404&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13854&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EOTGL-01</t>
+          <t>EOTSC-06</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>짐 글러브 2.0</t>
+          <t>서포트 쿠션 러닝 삭스</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>21,000</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>715</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8838&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13404&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EMTSV-03</t>
+          <t>EOTGL-01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 무릎 보호대</t>
+          <t>짐 글러브 2.0</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>21,000</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1,917</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13854&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8838&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EOTSC-06</t>
+          <t>EMTSV-03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>서포트 쿠션 러닝 삭스</t>
+          <t>[1&amp;1] 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2129,138 +2129,138 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>1,917</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9620&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6952&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EMTBG-12</t>
+          <t>EJFST-02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>데일리 쇼퍼백</t>
+          <t>릴렉스 요가링</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1,339</t>
+          <t>6,445</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6952&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14084&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EJFST-02</t>
+          <t>EOTET-01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>릴렉스 요가링</t>
+          <t>소프트 뱀부 롱 타월</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3,900</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>6,442</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14084&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9620&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EOTET-01</t>
+          <t>EMTBG-12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>소프트 뱀부 롱 타월</t>
+          <t>데일리 쇼퍼백</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>1,339</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>680</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2393,163 +2393,163 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16844&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15409&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EPTET-02</t>
+          <t>EOTSC-15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>언더웨어 세탁망</t>
+          <t>논슬립 퍼포먼스 풀 토삭스</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10554&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16844&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ENTMK-01</t>
+          <t>EPTET-02</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>UV 프로텍션 맨즈 골프 마스크</t>
+          <t>언더웨어 세탁망</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>22,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1,508</t>
+          <t>236</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15409&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10940&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EOTSC-15</t>
+          <t>ENTBG-03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 풀 토삭스</t>
+          <t>데일리 스트링 쇼퍼백</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>63,000</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>628</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17407&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10554&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EPTBG-04</t>
+          <t>ENTMK-01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>드라이 페더 버킷백</t>
+          <t>UV 프로텍션 맨즈 골프 마스크</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>52,000</t>
+          <t>22,000</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>1,508</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2561,121 +2561,121 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17437&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17407&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EPTCP-03</t>
+          <t>EPTBG-04</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>썬가드 와이드 버킷햇</t>
+          <t>드라이 페더 버킷백</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>52,000</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>51</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10940&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13853&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ENTBG-03</t>
+          <t>EOTBG-12</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>데일리 스트링 쇼퍼백</t>
+          <t>프리런 벨크로 러닝 벨트</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>63,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13853&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8726&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EOTBG-12</t>
+          <t>EMTSC-03</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>프리런 벨크로 러닝 벨트</t>
+          <t>논슬립 서포트 풀 토삭스 (HOLE)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>4,741</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2687,79 +2687,79 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8726&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17437&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EMTSC-03</t>
+          <t>EPTCP-03</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>논슬립 서포트 풀 토삭스 (HOLE)</t>
+          <t>썬가드 와이드 버킷햇</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>4,741</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15403&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16649&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EOTBG-21</t>
+          <t>EPTBG-02</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>데일리 라운드백</t>
+          <t>서밋 유틸리티 백팩</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>75,000</t>
+          <t>89,000</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>64,000</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2771,84 +2771,84 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16649&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16868&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EPTBG-02</t>
+          <t>EPTBG-03</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>서밋 유틸리티 백팩</t>
+          <t>컴팩트 포켓 크로스백</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>89,000</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>62,000</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16868&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15403&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EPTBG-03</t>
+          <t>EOTBG-21</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>컴팩트 포켓 크로스백</t>
+          <t>데일리 라운드백</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>75,000</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>62,000</t>
+          <t>64,000</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -2897,121 +2897,121 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15144&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17446&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EOTBO-01</t>
+          <t>EPTSV-01</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>액티브 스포츠 보틀 (650ml)</t>
+          <t>[1&amp;1] 3D 쿨링 핑거홀 팔토시</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>31,800</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>26,900</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17446&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15144&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EPTSV-01</t>
+          <t>EOTBO-01</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>[1&amp;1] 3D 쿨링 핑거홀 팔토시</t>
+          <t>액티브 스포츠 보틀 (650ml)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>31,800</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>26,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>77</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6660&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16631&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EKPMT-03</t>
+          <t>EPTSV-03</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>릴렉스 논슬립 요가 타월</t>
+          <t>컴프레션 카프 슬리브 (종아리 보호대)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>35,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1,506</t>
+          <t>182</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3023,37 +3023,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16631&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6660&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EPTSV-03</t>
+          <t>EKPMT-03</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>컴프레션 카프 슬리브 (종아리 보호대)</t>
+          <t>릴렉스 논슬립 요가 타월</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>35,900</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>1,508</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3107,163 +3107,163 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12318&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13604&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ENTBG-13</t>
+          <t>EOTSV-01</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>데일리 스퀘어백</t>
+          <t>[1&amp;1] 하이 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>661</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15408&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15145&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EOTSC-14</t>
+          <t>EOTBG-18</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>맨즈 논슬립 풀 토삭스</t>
+          <t>액티브 메쉬쿠션 슬링백</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13604&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15408&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EOTSV-01</t>
+          <t>EOTSC-14</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[1&amp;1] 하이 서포트 무릎 보호대</t>
+          <t>맨즈 논슬립 풀 토삭스</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9989&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13407&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EMTET-02</t>
+          <t>EOTSV-03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>소프트 쿠셔닝 훌라후프</t>
+          <t>서포트 허리 보호대</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3317,17 +3317,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15145&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12318&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EOTBG-18</t>
+          <t>ENTBG-13</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>액티브 메쉬쿠션 슬링백</t>
+          <t>데일리 스퀘어백</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3337,59 +3337,59 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13407&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11456&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EOTSV-03</t>
+          <t>ENTSC-13</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>서포트 허리 보호대</t>
+          <t>[1&amp;1] 논슬립 퍼포먼스 삭스</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>17,800</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>2,990</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3401,163 +3401,163 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13408&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11456&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EOTSC-01</t>
+          <t>ENTSC-14</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>프레시 필드 니삭스</t>
+          <t>[1&amp;1] 논슬립 퍼포먼스 삭스</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>17,800</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>2,990</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15370&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EOTBG-14</t>
+          <t>EOTSC-16</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>폴더블 캐리백 2.0</t>
+          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>25,800</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>466</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11456&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ENTSC-13</t>
+          <t>EOTSC-17</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 퍼포먼스 삭스</t>
+          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>25,800</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>17,800</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2,988</t>
+          <t>466</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11456&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9989&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ENTSC-14</t>
+          <t>EMTET-02</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 퍼포먼스 삭스</t>
+          <t>소프트 쿠셔닝 훌라후프</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>17,800</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2,988</t>
+          <t>570</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3569,37 +3569,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13408&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EOTSC-16</t>
+          <t>EOTSC-01</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
+          <t>프레시 필드 니삭스</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>25,800</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>286</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3611,42 +3611,42 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15370&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EOTSC-17</t>
+          <t>EOTBG-14</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
+          <t>폴더블 캐리백 2.0</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>25,800</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>64</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -3821,37 +3821,37 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13859&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8621&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ENTSO-12</t>
+          <t>EMTSV-06</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>안다르 제트플라이 (맨즈)</t>
+          <t>에어쿨링 손목 보호대</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>1,049</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3863,37 +3863,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8621&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13859&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EMTSV-06</t>
+          <t>ENTSO-12</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>에어쿨링 손목 보호대</t>
+          <t>안다르 제트플라이 (맨즈)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1,048</t>
+          <t>687</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3905,163 +3905,163 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6661&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10948&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EKPMB-01</t>
+          <t>ENTSC-20</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>릴렉스 웨이트볼 0.5kg</t>
+          <t>시그니처 로고 크루 삭스</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>531</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17436&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11027&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EPTSV-01</t>
+          <t>ENTSC-08</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>3D 쿨링 핑거홀 팔토시</t>
+          <t>[5 SET] 에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>794</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11027&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6661&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ENTSC-08</t>
+          <t>EKPMB-01</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>[5 SET] 에어컴피 크루 삭스</t>
+          <t>릴렉스 웨이트볼 0.5kg</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>6,500</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>649</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17436&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ENTSV-01</t>
+          <t>EPTSV-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>[1&amp;1] 3D 쿨링 팔토시</t>
+          <t>3D 쿨링 핑거홀 팔토시</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>25,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4073,84 +4073,84 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10948&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11362&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ENTSC-20</t>
+          <t>ENTBG-06</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>시그니처 로고 크루 삭스</t>
+          <t>올데이 투웨이 슬링백</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5837&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EJFMB-03</t>
+          <t>ENTSV-01</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>릴렉스 짐볼 65cm</t>
+          <t>[1&amp;1] 3D 쿨링 팔토시</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>25,900</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2,067</t>
+          <t>528</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -4199,121 +4199,121 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11096&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ENTSC-19</t>
+          <t>ENTSC-10</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
+          <t>더블 링글 라이트 크루 삭스</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>834</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5837&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EOTSC-14</t>
+          <t>EJFMB-03</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
+          <t>릴렉스 짐볼 65cm</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>2,067</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15428&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EOTBG-20</t>
+          <t>ENTSC-19</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>클라우드 스트링 쇼퍼백</t>
+          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>67,000</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4325,42 +4325,42 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11362&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ENTBG-06</t>
+          <t>EOTSC-14</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>올데이 투웨이 슬링백</t>
+          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -4409,121 +4409,121 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11096&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15428&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ENTSC-10</t>
+          <t>EOTBG-20</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>더블 링글 라이트 크루 삭스</t>
+          <t>클라우드 스트링 쇼퍼백</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>67,000</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9996&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8578&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EMTSC-27</t>
+          <t>EMTSC-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>올라운드 오버 니삭스</t>
+          <t>링글 크루 삭스</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>1,293</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EPTFB-02</t>
+          <t>EMTSC-05</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>퍼포먼스 심리스 손목밴드</t>
+          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>539</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4535,79 +4535,79 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16632&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EMTSC-05</t>
+          <t>EPTSV-02</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
+          <t>[1&amp;1] 하이 서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EMTSC-04</t>
+          <t>EPTFB-02</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
+          <t>퍼포먼스 심리스 손목밴드</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>186</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4661,69 +4661,69 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16632&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>EPTSV-02</t>
+          <t>EMTSC-04</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>[1&amp;1] 하이 서포트 발목 보호대</t>
+          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>635</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8578&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11061&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EMTSC-01</t>
+          <t>ENTSV-01</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>링글 크루 삭스</t>
+          <t>3D 쿨링 팔토시</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4733,49 +4733,49 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1,293</t>
+          <t>528</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6828&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11085&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EKPET-01</t>
+          <t>ENTET-01</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>[1&amp;1] 릴렉스 소프트 웨이트바 1kg</t>
+          <t>소프트 뱀부 스포츠 타월</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>41,800</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>37,600</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>327</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4787,42 +4787,42 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11061&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6828&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ENTSV-01</t>
+          <t>EKPET-01</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>3D 쿨링 팔토시</t>
+          <t>[1&amp;1] 릴렉스 소프트 웨이트바 1kg</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>41,800</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>37,600</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>583</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>163</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4871,42 +4871,42 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11085&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10953&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ENTET-01</t>
+          <t>ENTSC-07</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>소프트 뱀부 스포츠 타월</t>
+          <t>[3 SET] 에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>51,000</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>22,000</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>549</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -4955,84 +4955,84 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10953&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6665&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ENTSC-07</t>
+          <t>EKPRB-05</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>[3 SET] 에어컴피 크루 삭스</t>
+          <t>릴렉스 4레벨 힙 밴드</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>51,000</t>
+          <t>21,900</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>22,000</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>512</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6662&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15375&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EKPMB-02</t>
+          <t>EOTSC-16</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>릴렉스 미니 짐볼</t>
+          <t>논슬립 스킨 하프 토삭스</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>11,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>1,207</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>229</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>579</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>342</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5165,101 +5165,101 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15375&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14076&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EOTSC-16</t>
+          <t>EOTBG-13</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>논슬립 스킨 하프 토삭스</t>
+          <t>멀티 포켓 숄더 앤 크로스백</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>63,000</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>54,000</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>394</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14076&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8837&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EOTBG-13</t>
+          <t>EMTSV-02</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>멀티 포켓 숄더 앤 크로스백</t>
+          <t>[1&amp;1] 서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>63,000</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>54,000</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>689</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8837&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8836&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EMTSV-02</t>
+          <t>EMTSV-01</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 발목 보호대</t>
+          <t>[1&amp;1] 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>580</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5291,121 +5291,121 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6665&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12096&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EKPRB-05</t>
+          <t>ENTET-02</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>릴렉스 4레벨 힙 밴드</t>
+          <t>릴렉스 소프트 웨이트바 2kg</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>21,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12096&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13805&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ENTET-02</t>
+          <t>EOTSC-04</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>릴렉스 소프트 웨이트바 2kg</t>
+          <t>올데이 수피마 스니커즈 삭스</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>31,000</t>
+          <t>4,500</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>410</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8836&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13806&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EMTSV-01</t>
+          <t>EOTSC-05</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 팔꿈치 보호대</t>
+          <t>올데이 수피마 앵클 삭스</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>451</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5501,22 +5501,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11457&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11458&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ENTSC-12</t>
+          <t>ENTSC-13</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 토삭스</t>
+          <t>논슬립 퍼포먼스 크루삭스</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>4,129</t>
+          <t>659</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5543,37 +5543,37 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13806&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11457&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EOTSC-05</t>
+          <t>ENTSC-12</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>올데이 수피마 앵클 삭스</t>
+          <t>논슬립 퍼포먼스 토삭스</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>4,129</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5585,37 +5585,37 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11458&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16847&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ENTSC-13</t>
+          <t>EPTSC-02</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 크루삭스</t>
+          <t>하이 쿠션 테이핑 러닝 삭스</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5627,37 +5627,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13805&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13605&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EOTSC-04</t>
+          <t>EOTSV-02</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>올데이 수피마 스니커즈 삭스</t>
+          <t>[1&amp;1] 하이 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>4,500</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5669,37 +5669,37 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16033&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10657&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EOTMK-02</t>
+          <t>EMTSC-17</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>소프텐션 넥마스크</t>
+          <t>[3 SET] 맨즈 클래식 삭스</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>20,700</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5711,37 +5711,37 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13605&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16033&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EOTSV-02</t>
+          <t>EOTMK-02</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>[1&amp;1] 하이 서포트 팔꿈치 보호대</t>
+          <t>소프텐션 넥마스크</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5753,79 +5753,79 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10657&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6662&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EMTSC-17</t>
+          <t>EKPMB-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>[3 SET] 맨즈 클래식 삭스</t>
+          <t>릴렉스 미니 짐볼</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>20,700</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>11,000</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>1,207</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16847&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17415&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EPTSC-02</t>
+          <t>EPTSC-01</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>하이 쿠션 테이핑 러닝 삭스</t>
+          <t>쿨 메쉬 서포트 러닝 삭스</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5837,37 +5837,37 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17415&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13405&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EPTSC-01</t>
+          <t>EOTSV-01</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>쿨 메쉬 서포트 러닝 삭스</t>
+          <t>하이 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>661</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5921,17 +5921,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8770&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9996&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>EMTSV-03</t>
+          <t>EMTSC-27</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>서포트 무릎 보호대</t>
+          <t>올라운드 오버 니삭스</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -5941,22 +5941,22 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>1,917</t>
+          <t>289</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -6005,22 +6005,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13405&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8770&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>EOTSV-01</t>
+          <t>EMTSV-03</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>하이 서포트 무릎 보호대</t>
+          <t>서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6030,17 +6030,17 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>1,917</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
@@ -6089,37 +6089,37 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>EMTSV-02</t>
+          <t>EOTSC-17</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>서포트 발목 보호대</t>
+          <t>논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6131,37 +6131,37 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>EOTSC-17</t>
+          <t>EMTSV-02</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>논슬립 스킨 토삭스</t>
+          <t>서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
+          <t>13,900</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
           <t>12,900</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>10,900</t>
-        </is>
-      </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>689</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6173,17 +6173,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13831&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16640&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EOTCP-02</t>
+          <t>EPTBG-05</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>데님 로고 볼캡</t>
+          <t>안다르 시그니처 로고 에코백</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.4</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>583</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6593,37 +6593,37 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8768&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16031&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>EMTSV-01</t>
+          <t>EOTGL-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>서포트 팔꿈치 보호대</t>
+          <t>히트 런 글러브</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>207</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6635,27 +6635,27 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16031&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13831&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>EOTGL-02</t>
+          <t>EOTCP-02</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>히트 런 글러브</t>
+          <t>데님 로고 볼캡</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -6665,54 +6665,54 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16640&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8768&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EPTBG-05</t>
+          <t>EMTSV-01</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>안다르 시그니처 로고 에코백</t>
+          <t>서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>580</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -6887,37 +6887,37 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15732&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13406&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>EOTSC-11</t>
+          <t>EOTSV-02</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>웜 레그 롱 워머</t>
+          <t>하이 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6929,27 +6929,27 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16034&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15732&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EOTGL-03</t>
+          <t>EOTSC-11</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>소프트 니트 플립 글러브</t>
+          <t>웜 레그 롱 워머</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6959,39 +6959,39 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16036&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16034&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EOTCP-06</t>
+          <t>EOTGL-03</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>소프트 니트 버킷햇</t>
+          <t>소프트 니트 플립 글러브</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -7001,39 +7001,39 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12795&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16036&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ENTCP-05</t>
+          <t>EOTCP-06</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>소프트 니트 비니</t>
+          <t>소프트 니트 버킷햇</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>51</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -7097,84 +7097,84 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17386&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10939&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EPTSC-07</t>
+          <t>ENTSC-07</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>맨즈 필라테스 앵클 삭스</t>
+          <t>에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>549</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13406&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9599&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EOTSV-02</t>
+          <t>EMTSC-28</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>하이 서포트 팔꿈치 보호대</t>
+          <t>리브드 셔링 루즈 삭스</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -7223,69 +7223,69 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9599&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17386&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EMTSC-28</t>
+          <t>EPTSC-07</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>리브드 셔링 루즈 삭스</t>
+          <t>맨즈 필라테스 앵클 삭스</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12783&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12795&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ENTSC-26</t>
+          <t>ENTCP-05</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>니트 기모 오버 니삭스</t>
+          <t>소프트 니트 비니</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7295,39 +7295,39 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>361</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15734&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12783&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EOTSC-20</t>
+          <t>ENTSC-26</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>레그 미들 워머</t>
+          <t>니트 기모 오버 니삭스</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7337,49 +7337,49 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>354</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10939&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15734&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ENTSC-07</t>
+          <t>EOTSC-20</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>에어컴피 크루 삭스</t>
+          <t>레그 미들 워머</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7433,27 +7433,27 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16035&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9993&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>EOTSC-12</t>
+          <t>EMTSC-29</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>소프트 니트 기모 니삭스</t>
+          <t>니트 루즈 삭스</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7463,39 +7463,39 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>512</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15865&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16035&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>EOTSC-18</t>
+          <t>EOTSC-12</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>올데이 기모 삭스</t>
+          <t>소프트 니트 기모 니삭스</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7505,39 +7505,39 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12480&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15865&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ENTSC-24</t>
+          <t>EOTSC-18</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>웜 슬릿 레그 워머</t>
+          <t>올데이 기모 삭스</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7547,86 +7547,86 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11375&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12480&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ENTSC-03</t>
+          <t>ENTSC-24</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>[3 SET] 에어프레시 페이크 삭스</t>
+          <t>웜 슬릿 레그 워머</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11374&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11375&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ENTSC-04</t>
+          <t>ENTSC-03</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>[7 SET] 에어프레시 페이크 삭스</t>
+          <t>[3 SET] 에어프레시 페이크 삭스</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>105,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -7643,32 +7643,32 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11373&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11374&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ENTSC-02</t>
+          <t>ENTSC-04</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>에어프레시 페이크 삭스</t>
+          <t>[7 SET] 에어프레시 페이크 삭스</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>105,000</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -7685,37 +7685,37 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10489&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11373&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>EMTRI-02</t>
+          <t>ENTSC-02</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>서스테이너블 뉴웨이브 요가링</t>
+          <t>에어프레시 페이크 삭스</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>15,000</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>33,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>640</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -7727,37 +7727,37 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10191&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10489&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>EMTSC-26</t>
+          <t>EMTRI-02</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>[1&amp;1] 램스울 크루 삭스</t>
+          <t>서스테이너블 뉴웨이브 요가링</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>33,000</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -7769,37 +7769,37 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9993&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10191&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>EMTSC-29</t>
+          <t>EMTSC-26</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>니트 루즈 삭스</t>
+          <t>[1&amp;1] 램스울 크루 삭스</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>19,800</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>736</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
